--- a/BioTern/assets/OJT MOCK UP.xlsx
+++ b/BioTern/assets/OJT MOCK UP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\BioTern\BioTern\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5C772E0-CCCA-4760-B523-CFA307F108E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8B5DFA-63E0-4B89-847F-B23F89B8942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="823">
   <si>
     <t>student_no</t>
   </si>
@@ -1916,9 +1916,6 @@
     <t>05-8366</t>
   </si>
   <si>
-    <t>05-8234</t>
-  </si>
-  <si>
     <t>05-9129</t>
   </si>
   <si>
@@ -2505,6 +2502,9 @@
   </si>
   <si>
     <t>1st FLOOR PARAGON, BUILDING, MON TANG AVE. BALIBAGO, ANGELES CITY</t>
+  </si>
+  <si>
+    <t>05-2387</t>
   </si>
 </sst>
 </file>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>626</v>
+        <v>822</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -3175,12 +3175,12 @@
         <v>17</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3256,7 +3256,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3484,7 +3484,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3555,12 +3555,12 @@
         <v>17</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3707,12 +3707,12 @@
         <v>17</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3750,7 +3750,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3788,7 +3788,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -4016,7 +4016,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -4049,12 +4049,12 @@
         <v>17</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -4087,12 +4087,12 @@
         <v>17</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4206,7 +4206,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4282,7 +4282,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4472,7 +4472,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4510,7 +4510,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4548,7 +4548,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4586,7 +4586,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4624,7 +4624,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4794,7 +4794,7 @@
         <v>200</v>
       </c>
       <c r="G50" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H50" t="s">
         <v>202</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4852,7 +4852,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4890,7 +4890,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4928,7 +4928,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -5004,7 +5004,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -5080,7 +5080,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5113,12 +5113,12 @@
         <v>17</v>
       </c>
       <c r="L58" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5189,12 +5189,12 @@
         <v>17</v>
       </c>
       <c r="L60" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5270,7 +5270,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5346,7 +5346,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5536,7 +5536,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5569,12 +5569,12 @@
         <v>17</v>
       </c>
       <c r="L70" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5645,12 +5645,12 @@
         <v>17</v>
       </c>
       <c r="L72" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5688,7 +5688,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5726,7 +5726,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5759,12 +5759,12 @@
         <v>17</v>
       </c>
       <c r="L75" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5802,7 +5802,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5840,7 +5840,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5878,7 +5878,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5916,7 +5916,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5949,12 +5949,12 @@
         <v>17</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5992,7 +5992,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -6025,12 +6025,12 @@
         <v>17</v>
       </c>
       <c r="L82" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -6068,7 +6068,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6106,7 +6106,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6139,12 +6139,12 @@
         <v>17</v>
       </c>
       <c r="L85" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6177,12 +6177,12 @@
         <v>17</v>
       </c>
       <c r="L86" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6220,7 +6220,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6329,12 +6329,12 @@
         <v>17</v>
       </c>
       <c r="L90" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6367,12 +6367,12 @@
         <v>17</v>
       </c>
       <c r="L91" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6405,12 +6405,12 @@
         <v>17</v>
       </c>
       <c r="L92" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6443,12 +6443,12 @@
         <v>17</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6481,12 +6481,12 @@
         <v>17</v>
       </c>
       <c r="L94" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6519,12 +6519,12 @@
         <v>17</v>
       </c>
       <c r="L95" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6595,12 +6595,12 @@
         <v>17</v>
       </c>
       <c r="L97" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6638,7 +6638,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6676,7 +6676,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -6694,7 +6694,7 @@
         <v>368</v>
       </c>
       <c r="G100" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H100" t="s">
         <v>370</v>
@@ -6709,12 +6709,12 @@
         <v>17</v>
       </c>
       <c r="L100" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -6752,7 +6752,7 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B102" t="s">
         <v>13</v>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B103" t="s">
         <v>13</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -6861,12 +6861,12 @@
         <v>17</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -6904,7 +6904,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
@@ -6937,12 +6937,12 @@
         <v>17</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
@@ -6975,12 +6975,12 @@
         <v>17</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
@@ -7051,12 +7051,12 @@
         <v>17</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
@@ -7127,12 +7127,12 @@
         <v>17</v>
       </c>
       <c r="L111" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
@@ -7165,12 +7165,12 @@
         <v>17</v>
       </c>
       <c r="L112" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
@@ -7208,7 +7208,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B114" t="s">
         <v>13</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B115" t="s">
         <v>13</v>
@@ -7284,7 +7284,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B117" t="s">
         <v>13</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
@@ -7393,12 +7393,12 @@
         <v>17</v>
       </c>
       <c r="L118" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
@@ -7436,7 +7436,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
@@ -7507,12 +7507,12 @@
         <v>17</v>
       </c>
       <c r="L121" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B122" t="s">
         <v>13</v>
@@ -7545,12 +7545,12 @@
         <v>17</v>
       </c>
       <c r="L122" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
@@ -7583,12 +7583,12 @@
         <v>17</v>
       </c>
       <c r="L123" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B124" t="s">
         <v>13</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
@@ -7659,12 +7659,12 @@
         <v>17</v>
       </c>
       <c r="L125" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B126" t="s">
         <v>13</v>
@@ -7702,7 +7702,7 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B127" t="s">
         <v>13</v>
@@ -7740,7 +7740,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B128" t="s">
         <v>13</v>
@@ -7778,7 +7778,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B129" t="s">
         <v>13</v>
@@ -7816,7 +7816,7 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B130" t="s">
         <v>13</v>
@@ -7854,7 +7854,7 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B131" t="s">
         <v>13</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B132" t="s">
         <v>13</v>
@@ -7930,7 +7930,7 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B133" t="s">
         <v>13</v>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B134" t="s">
         <v>13</v>
@@ -8006,7 +8006,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B135" t="s">
         <v>13</v>
@@ -8044,7 +8044,7 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B136" t="s">
         <v>13</v>
@@ -8082,7 +8082,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B137" t="s">
         <v>13</v>
@@ -8120,7 +8120,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B138" t="s">
         <v>13</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B139" t="s">
         <v>13</v>
@@ -8196,7 +8196,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B140" t="s">
         <v>13</v>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B141" t="s">
         <v>13</v>
@@ -8272,7 +8272,7 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B142" t="s">
         <v>13</v>
@@ -8310,7 +8310,7 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B143" t="s">
         <v>13</v>
@@ -8348,7 +8348,7 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B144" t="s">
         <v>13</v>
@@ -8386,7 +8386,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B145" t="s">
         <v>13</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B146" t="s">
         <v>13</v>
@@ -8462,7 +8462,7 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B147" t="s">
         <v>13</v>
@@ -8500,7 +8500,7 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B148" t="s">
         <v>13</v>
@@ -8538,7 +8538,7 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B149" t="s">
         <v>13</v>
@@ -8576,7 +8576,7 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B150" t="s">
         <v>13</v>
@@ -8614,7 +8614,7 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B151" t="s">
         <v>13</v>
@@ -8652,7 +8652,7 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B152" t="s">
         <v>13</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B153" t="s">
         <v>13</v>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B154" t="s">
         <v>13</v>
@@ -8766,7 +8766,7 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B155" t="s">
         <v>13</v>
@@ -8804,7 +8804,7 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B156" t="s">
         <v>13</v>
@@ -8842,7 +8842,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B157" t="s">
         <v>13</v>
@@ -8880,7 +8880,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B158" t="s">
         <v>13</v>
@@ -8918,7 +8918,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B159" t="s">
         <v>13</v>
@@ -8951,12 +8951,12 @@
         <v>17</v>
       </c>
       <c r="L159" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B160" t="s">
         <v>13</v>
@@ -8989,12 +8989,12 @@
         <v>17</v>
       </c>
       <c r="L160" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B161" t="s">
         <v>13</v>
@@ -9032,7 +9032,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B162" t="s">
         <v>13</v>
@@ -9070,7 +9070,7 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B163" t="s">
         <v>13</v>
@@ -9108,7 +9108,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B164" t="s">
         <v>13</v>
@@ -9146,7 +9146,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B165" t="s">
         <v>13</v>
@@ -9184,7 +9184,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B166" t="s">
         <v>13</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B167" t="s">
         <v>13</v>
@@ -9260,7 +9260,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B168" t="s">
         <v>13</v>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B169" t="s">
         <v>13</v>
@@ -9336,7 +9336,7 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B170" t="s">
         <v>13</v>
@@ -9374,7 +9374,7 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B171" t="s">
         <v>13</v>
@@ -9412,7 +9412,7 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B172" t="s">
         <v>13</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B173" t="s">
         <v>13</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B174" t="s">
         <v>13</v>
@@ -9526,7 +9526,7 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B175" t="s">
         <v>13</v>
@@ -9564,7 +9564,7 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B176" t="s">
         <v>13</v>
@@ -9602,7 +9602,7 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B177" t="s">
         <v>13</v>
@@ -9640,7 +9640,7 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B178" t="s">
         <v>13</v>
@@ -9678,7 +9678,7 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B179" t="s">
         <v>13</v>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B180" t="s">
         <v>13</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B181" t="s">
         <v>13</v>
@@ -9792,7 +9792,7 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B182" t="s">
         <v>13</v>
@@ -9830,7 +9830,7 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B183" t="s">
         <v>13</v>
@@ -9868,7 +9868,7 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B184" t="s">
         <v>13</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B185" t="s">
         <v>13</v>
@@ -9944,7 +9944,7 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B186" t="s">
         <v>13</v>
@@ -9982,7 +9982,7 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B187" t="s">
         <v>13</v>
@@ -10020,7 +10020,7 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B188" t="s">
         <v>13</v>
@@ -10058,7 +10058,7 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B189" t="s">
         <v>13</v>
@@ -10096,7 +10096,7 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B190" t="s">
         <v>13</v>
@@ -10134,7 +10134,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B191" t="s">
         <v>13</v>
@@ -10172,7 +10172,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B192" t="s">
         <v>13</v>
@@ -10210,7 +10210,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B193" t="s">
         <v>13</v>
@@ -10248,7 +10248,7 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B194" t="s">
         <v>13</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B195" t="s">
         <v>13</v>
@@ -10324,7 +10324,7 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B196" t="s">
         <v>13</v>
@@ -10362,7 +10362,7 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B197" t="s">
         <v>13</v>
@@ -10400,7 +10400,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B198" t="s">
         <v>13</v>
@@ -10438,7 +10438,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B199" t="s">
         <v>13</v>

--- a/BioTern/assets/OJT MOCK UP.xlsx
+++ b/BioTern/assets/OJT MOCK UP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\BioTern\BioTern\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8B5DFA-63E0-4B89-847F-B23F89B8942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E296954-08F6-45F3-B7B4-B4BE07A75DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2264,9 +2264,6 @@
     <t>05-90199</t>
   </si>
   <si>
-    <t>05-90200</t>
-  </si>
-  <si>
     <t>05-90201</t>
   </si>
   <si>
@@ -2505,6 +2502,9 @@
   </si>
   <si>
     <t>05-2387</t>
+  </si>
+  <si>
+    <t>05-8377</t>
   </si>
 </sst>
 </file>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -3175,7 +3175,7 @@
         <v>17</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -3555,7 +3555,7 @@
         <v>17</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -3707,7 +3707,7 @@
         <v>17</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -4049,7 +4049,7 @@
         <v>17</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -4087,7 +4087,7 @@
         <v>17</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -4794,7 +4794,7 @@
         <v>200</v>
       </c>
       <c r="G50" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H50" t="s">
         <v>202</v>
@@ -5113,7 +5113,7 @@
         <v>17</v>
       </c>
       <c r="L58" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -5189,7 +5189,7 @@
         <v>17</v>
       </c>
       <c r="L60" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -5569,7 +5569,7 @@
         <v>17</v>
       </c>
       <c r="L70" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -5645,7 +5645,7 @@
         <v>17</v>
       </c>
       <c r="L72" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -5759,7 +5759,7 @@
         <v>17</v>
       </c>
       <c r="L75" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -5949,7 +5949,7 @@
         <v>17</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -6025,7 +6025,7 @@
         <v>17</v>
       </c>
       <c r="L82" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -6139,7 +6139,7 @@
         <v>17</v>
       </c>
       <c r="L85" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -6177,7 +6177,7 @@
         <v>17</v>
       </c>
       <c r="L86" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -6329,7 +6329,7 @@
         <v>17</v>
       </c>
       <c r="L90" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -6367,7 +6367,7 @@
         <v>17</v>
       </c>
       <c r="L91" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -6405,7 +6405,7 @@
         <v>17</v>
       </c>
       <c r="L92" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -6443,7 +6443,7 @@
         <v>17</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -6481,7 +6481,7 @@
         <v>17</v>
       </c>
       <c r="L94" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -6519,7 +6519,7 @@
         <v>17</v>
       </c>
       <c r="L95" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -6595,7 +6595,7 @@
         <v>17</v>
       </c>
       <c r="L97" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -6694,7 +6694,7 @@
         <v>368</v>
       </c>
       <c r="G100" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H100" t="s">
         <v>370</v>
@@ -6709,7 +6709,7 @@
         <v>17</v>
       </c>
       <c r="L100" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -6861,7 +6861,7 @@
         <v>17</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -6937,7 +6937,7 @@
         <v>17</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -6975,7 +6975,7 @@
         <v>17</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -7051,7 +7051,7 @@
         <v>17</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -7127,7 +7127,7 @@
         <v>17</v>
       </c>
       <c r="L111" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -7165,7 +7165,7 @@
         <v>17</v>
       </c>
       <c r="L112" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -7393,7 +7393,7 @@
         <v>17</v>
       </c>
       <c r="L118" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -7507,7 +7507,7 @@
         <v>17</v>
       </c>
       <c r="L121" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -7545,12 +7545,12 @@
         <v>17</v>
       </c>
       <c r="L122" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>742</v>
+        <v>822</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
@@ -7583,12 +7583,12 @@
         <v>17</v>
       </c>
       <c r="L123" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B124" t="s">
         <v>13</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
@@ -7659,12 +7659,12 @@
         <v>17</v>
       </c>
       <c r="L125" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B126" t="s">
         <v>13</v>
@@ -7702,7 +7702,7 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B127" t="s">
         <v>13</v>
@@ -7740,7 +7740,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B128" t="s">
         <v>13</v>
@@ -7778,7 +7778,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B129" t="s">
         <v>13</v>
@@ -7816,7 +7816,7 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B130" t="s">
         <v>13</v>
@@ -7854,7 +7854,7 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B131" t="s">
         <v>13</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B132" t="s">
         <v>13</v>
@@ -7930,7 +7930,7 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B133" t="s">
         <v>13</v>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B134" t="s">
         <v>13</v>
@@ -8006,7 +8006,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B135" t="s">
         <v>13</v>
@@ -8044,7 +8044,7 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B136" t="s">
         <v>13</v>
@@ -8082,7 +8082,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B137" t="s">
         <v>13</v>
@@ -8120,7 +8120,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B138" t="s">
         <v>13</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B139" t="s">
         <v>13</v>
@@ -8196,7 +8196,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B140" t="s">
         <v>13</v>
@@ -8234,7 +8234,7 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B141" t="s">
         <v>13</v>
@@ -8272,7 +8272,7 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B142" t="s">
         <v>13</v>
@@ -8310,7 +8310,7 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B143" t="s">
         <v>13</v>
@@ -8348,7 +8348,7 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B144" t="s">
         <v>13</v>
@@ -8386,7 +8386,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B145" t="s">
         <v>13</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B146" t="s">
         <v>13</v>
@@ -8462,7 +8462,7 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B147" t="s">
         <v>13</v>
@@ -8500,7 +8500,7 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B148" t="s">
         <v>13</v>
@@ -8538,7 +8538,7 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B149" t="s">
         <v>13</v>
@@ -8576,7 +8576,7 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B150" t="s">
         <v>13</v>
@@ -8614,7 +8614,7 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B151" t="s">
         <v>13</v>
@@ -8652,7 +8652,7 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B152" t="s">
         <v>13</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B153" t="s">
         <v>13</v>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B154" t="s">
         <v>13</v>
@@ -8766,7 +8766,7 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B155" t="s">
         <v>13</v>
@@ -8804,7 +8804,7 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B156" t="s">
         <v>13</v>
@@ -8842,7 +8842,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B157" t="s">
         <v>13</v>
@@ -8880,7 +8880,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B158" t="s">
         <v>13</v>
@@ -8918,7 +8918,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B159" t="s">
         <v>13</v>
@@ -8951,12 +8951,12 @@
         <v>17</v>
       </c>
       <c r="L159" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B160" t="s">
         <v>13</v>
@@ -8989,12 +8989,12 @@
         <v>17</v>
       </c>
       <c r="L160" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B161" t="s">
         <v>13</v>
@@ -9032,7 +9032,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B162" t="s">
         <v>13</v>
@@ -9070,7 +9070,7 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B163" t="s">
         <v>13</v>
@@ -9108,7 +9108,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B164" t="s">
         <v>13</v>
@@ -9146,7 +9146,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B165" t="s">
         <v>13</v>
@@ -9184,7 +9184,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B166" t="s">
         <v>13</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B167" t="s">
         <v>13</v>
@@ -9260,7 +9260,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B168" t="s">
         <v>13</v>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B169" t="s">
         <v>13</v>
@@ -9336,7 +9336,7 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B170" t="s">
         <v>13</v>
@@ -9374,7 +9374,7 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B171" t="s">
         <v>13</v>
@@ -9412,7 +9412,7 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B172" t="s">
         <v>13</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B173" t="s">
         <v>13</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B174" t="s">
         <v>13</v>
@@ -9526,7 +9526,7 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B175" t="s">
         <v>13</v>
@@ -9564,7 +9564,7 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B176" t="s">
         <v>13</v>
@@ -9602,7 +9602,7 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B177" t="s">
         <v>13</v>
@@ -9640,7 +9640,7 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B178" t="s">
         <v>13</v>
@@ -9678,7 +9678,7 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B179" t="s">
         <v>13</v>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B180" t="s">
         <v>13</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B181" t="s">
         <v>13</v>
@@ -9792,7 +9792,7 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B182" t="s">
         <v>13</v>
@@ -9830,7 +9830,7 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B183" t="s">
         <v>13</v>
@@ -9868,7 +9868,7 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B184" t="s">
         <v>13</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B185" t="s">
         <v>13</v>
@@ -9944,7 +9944,7 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B186" t="s">
         <v>13</v>
@@ -9982,7 +9982,7 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B187" t="s">
         <v>13</v>
@@ -10020,7 +10020,7 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B188" t="s">
         <v>13</v>
@@ -10058,7 +10058,7 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B189" t="s">
         <v>13</v>
@@ -10096,7 +10096,7 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B190" t="s">
         <v>13</v>
@@ -10134,7 +10134,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B191" t="s">
         <v>13</v>
@@ -10172,7 +10172,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B192" t="s">
         <v>13</v>
@@ -10210,7 +10210,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B193" t="s">
         <v>13</v>
@@ -10248,7 +10248,7 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B194" t="s">
         <v>13</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B195" t="s">
         <v>13</v>
@@ -10324,7 +10324,7 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B196" t="s">
         <v>13</v>
@@ -10362,7 +10362,7 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B197" t="s">
         <v>13</v>
@@ -10400,7 +10400,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B198" t="s">
         <v>13</v>
@@ -10438,7 +10438,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B199" t="s">
         <v>13</v>
